--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_灵魂配置表_Manufacture_SoulConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_灵魂配置表_Manufacture_SoulConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="81">
   <si>
     <t>灵魂ID</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parabola</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1389,7 @@
         <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
